--- a/导入模板.xlsx
+++ b/导入模板.xlsx
@@ -505,28 +505,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>门店名称：必填，门店全称</t>
+          <t>门店名称：必填</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>可容纳人数：必填，数字（如 2、3）</t>
+          <t>可容纳人数：必填，数字</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>适配范围：必填，填写"服务"或"非服务"</t>
+          <t>适配范围：必填，"服务"或"非服务"</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>请删除示例数据后填写真实数据</t>
+          <t>请删除示例数据后填写</t>
         </is>
       </c>
     </row>
@@ -541,12 +541,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,6 +571,36 @@
           <t>类型</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>职位名称</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>一级部门</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>二级部门</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>三级部门</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>四级部门</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>五级部门</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -582,6 +618,32 @@
           <t>服务</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>服务工程师</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>中国区</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>服务部</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>北京服务中心</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>海淀服务站</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -599,6 +661,32 @@
           <t>服务</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>店员</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>中国区</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>服务部</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>北京服务中心</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>朝阳服务站</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -616,6 +704,28 @@
           <t>非服务</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>运营专员</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>中国区</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>运营部</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>北京运营中心</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -633,6 +743,32 @@
           <t>非服务</t>
         </is>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>销售顾问</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>中国区</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>北京销售中心</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>海淀销售站</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -644,28 +780,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>工号：必填，唯一标识</t>
+          <t>工号、姓名、类型：必填</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>姓名：必填</t>
+          <t>职位名称、一级~五级部门：选填</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>类型：必填，填写"服务"或"非服务"</t>
+          <t>类型：填"服务"或"非服务"</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>请删除示例数据后填写真实数据</t>
+          <t>请删除示例数据后填写</t>
         </is>
       </c>
     </row>
